--- a/nriss-patch-2/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:58:47+00:00</t>
+    <t>2026-08-04T07:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-2/ig/StructureDefinition-fr-device-use-statement-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-device-use-statement-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$44</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1754" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="301">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T07:44:41+00:00</t>
+    <t>2026-08-07T09:15:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -895,7 +895,7 @@
     <t>DeviceUseStatement.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1|Media|4.0.1)
+    <t xml:space="preserve">Reference(Observation|4.0.1|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-condition-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-prevention-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-ald-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-work-related-accident-document|0.1.0)
 </t>
   </si>
   <si>
@@ -905,10 +905,6 @@
     <t>Indicates another resource whose existence justifies this DeviceUseStatement.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:resolve().code}
-</t>
-  </si>
-  <si>
     <t>Event.reasonReference</t>
   </si>
   <si>
@@ -916,41 +912,6 @@
   </si>
   <si>
     <t>.outboundRelationship[typeCode=RSON].target</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.reasonReference:EnRapportAvecALD</t>
-  </si>
-  <si>
-    <t>EnRapportAvecALD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-condition-document|0.1.0)
-</t>
-  </si>
-  <si>
-    <t>Observation indiquant que l'utilisation est en rapport avec une ALD</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.reasonReference:EnRapportAvecAccidentTravail</t>
-  </si>
-  <si>
-    <t>EnRapportAvecAccidentTravail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-work-related-accident-document|0.1.0)
-</t>
-  </si>
-  <si>
-    <t>Observation indiquant que l'utilisation est en rapport avec un accident de travail</t>
-  </si>
-  <si>
-    <t>DeviceUseStatement.reasonReference:EnRapportAvecLaPrevention</t>
-  </si>
-  <si>
-    <t>EnRapportAvecLaPrevention</t>
-  </si>
-  <si>
-    <t>Observation indiquant que l'utilisation est liée à la prévention</t>
   </si>
   <si>
     <t>DeviceUseStatement.bodySite</t>
@@ -1310,12 +1271,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO47"/>
+  <dimension ref="A1:AO44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="58.55859375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="42.046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="25.1484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -6114,7 +6075,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>280</v>
       </c>
@@ -6187,14 +6148,16 @@
         <v>78</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AC42" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>280</v>
@@ -6212,7 +6175,7 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>78</v>
@@ -6221,22 +6184,20 @@
         <v>279</v>
       </c>
       <c r="AN42" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AO42" t="s" s="2">
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
         <v>287</v>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>288</v>
-      </c>
       <c r="B43" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>78</v>
       </c>
@@ -6248,7 +6209,7 @@
         <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>78</v>
@@ -6257,16 +6218,18 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L43" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
       </c>
@@ -6290,13 +6253,13 @@
         <v>78</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>78</v>
+        <v>291</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>78</v>
+        <v>292</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>78</v>
+        <v>293</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>78</v>
@@ -6314,13 +6277,13 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>78</v>
@@ -6329,31 +6292,29 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>279</v>
+        <v>78</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>286</v>
+        <v>78</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>78</v>
       </c>
@@ -6362,25 +6323,25 @@
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6431,7 +6392,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6446,372 +6407,23 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>78</v>
+        <v>300</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>279</v>
+        <v>78</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>286</v>
+        <v>78</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="D45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
-      <c r="P45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="46" hidden="true">
-      <c r="A46" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="P46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="47" hidden="true">
-      <c r="A47" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
-      <c r="P47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q47" s="2"/>
-      <c r="R47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO47" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO47">
+  <autoFilter ref="A1:AO44">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6821,7 +6433,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI46">
+  <conditionalFormatting sqref="A2:AI43">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
